--- a/site/SFTP-UKG-Pro-Integration-Setup-Guide/headings.xlsx
+++ b/site/SFTP-UKG-Pro-Integration-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,644 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>h_01JZW9E9B6ZZRTWQSYHXT2DAAF</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01JZW9E9B6ZZRTWQSYHXT2DAAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Key Functions</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01KG4G8M52X0H1382BKQAJQG71</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KG4G8M52X0H1382BKQAJQG71</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Integration Scenarios</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>General Settings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Synchronization Settings</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Worker Sync Settings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KPTQH26P3CR5WMNQEXQES2C0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTQH26P3CR5WMNQEXQES2C0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Candidate Management</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Writeback Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Notification Template Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Success Execution</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Failure Execution</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Worker to SFTP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Candidate to SFTP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Writeback Map</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/SFTP-UKG-Pro-Integration-Setup-Guide/headings.xlsx
+++ b/site/SFTP-UKG-Pro-Integration-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01KG4G8M52X0H1382BKQAJQG71</t>
+          <t>h_01M1EE04YEJMEN6RGKZDY0YC1A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KG4G8M52X0H1382BKQAJQG71</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01M1EE04YEJMEN6RGKZDY0YC1A</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>h_01M1GFR3W48XB1EMDYARC8WM65</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01M1GFR3W48XB1EMDYARC8WM65</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Synchronization Settings</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,41 +671,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Worker Sync Settings</t>
+          <t>Synchronization Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KPTQH26P3CR5WMNQEXQES2C0</t>
+          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTQH26P3CR5WMNQEXQES2C0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Candidate Management</t>
+          <t>Worker Sync Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
+          <t>h_01KPTQH26P3CR5WMNQEXQES2C0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTQH26P3CR5WMNQEXQES2C0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Writeback Settings</t>
+          <t>Candidate Management</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
+          <t>h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Writeback Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,41 +825,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,63 +913,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Worker to SFTP</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Candidate to SFTP</t>
+          <t>Worker to SFTP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Writeback Map</t>
+          <t>Candidate to SFTP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,76 +1001,98 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Writeback Map</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/SFTP-UKG-Pro-Integration-Setup-Guide/headings.xlsx
+++ b/site/SFTP-UKG-Pro-Integration-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,29 +683,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Synchronization Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Worker Sync Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,129 +715,129 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KPTQH26P3CR5WMNQEXQES2C0</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTQH26P3CR5WMNQEXQES2C0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Candidate Management</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Writeback Settings</t>
+          <t>Success / Successful Execution</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Failure / Failed Execution</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Skipping / Skipped Execution</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01M1K1HC212G052PS1DWHW150K</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01M1K1HC212G052PS1DWHW150K</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,100 +847,100 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>UKG to SAP Settings / Applications Setting / UKG to SFTP Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01M1K257ARHDGMXKEXB2SSG4RK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01M1K257ARHDGMXKEXB2SSG4RK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>UKG Pro Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>h_01M1K2A9SSG16Z8AM1VPT2FVWD</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01M1K2A9SSG16Z8AM1VPT2FVWD</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>SFTP Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01M1KAV7XJZ5EW8EVFR5ACHBC4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01M1KAV7XJZ5EW8EVFR5ACHBC4</t>
         </is>
       </c>
     </row>
@@ -969,130 +969,86 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Worker to SFTP</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Candidate to SFTP</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>h_01M1KAV7XJCAY9QWDWPM94JFX9</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01M1KAV7XJCAY9QWDWPM94JFX9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Writeback Map</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/SFTP-UKG-Pro-Integration-Setup-Guide/headings.xlsx
+++ b/site/SFTP-UKG-Pro-Integration-Setup-Guide/headings.xlsx
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Scenarios</t>
+          <t>Integration Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>h_01M1K1H860DYM4S4TCYBD7ESRJ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01M1K1H860DYM4S4TCYBD7ESRJ</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01M1KAV7XJZ5EW8EVFR5ACHBC4</t>
+          <t>h_01M1KTH2PCZEKKZD14ZS4TC38H</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01M1KAV7XJZ5EW8EVFR5ACHBC4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01M1KTH2PCZEKKZD14ZS4TC38H</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01M1KAV7XJCAY9QWDWPM94JFX9</t>
+          <t>h_01M1KTH2PCQA3C1VWVV451M0FJ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01M1KAV7XJCAY9QWDWPM94JFX9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SFTP-UKG-Pro-Integration-Setup-Guide/#h_01M1KTH2PCQA3C1VWVV451M0FJ</t>
         </is>
       </c>
     </row>

--- a/site/SFTP-UKG-Pro-Integration-Setup-Guide/headings.xlsx
+++ b/site/SFTP-UKG-Pro-Integration-Setup-Guide/headings.xlsx
@@ -881,7 +881,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UKG to SAP Settings / Applications Setting / UKG to SFTP Settings</t>
+          <t>UKG to SFTP Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">

--- a/site/SFTP-UKG-Pro-Integration-Setup-Guide/headings.xlsx
+++ b/site/SFTP-UKG-Pro-Integration-Setup-Guide/headings.xlsx
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Success / Successful Execution</t>
+          <t>Successful Execution</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Failure / Failed Execution</t>
+          <t>Failed Execution</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Skipping / Skipped Execution</t>
+          <t>Skipped Execution</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
